--- a/Enade_2016_Ifes.xlsx
+++ b/Enade_2016_Ifes.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,11 @@
           <t>Situação</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CAMPUS</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -561,6 +566,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Barra de São Francisco</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -616,6 +626,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -671,6 +686,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Guarapari</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -726,6 +746,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Linhares</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -781,6 +806,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Santa Maria de Jetibá</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -836,6 +866,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Venda Nova do Imigrante</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -891,6 +926,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -946,6 +986,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -999,6 +1044,11 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
         </is>
       </c>
     </row>
@@ -1056,6 +1106,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1111,6 +1166,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1166,6 +1226,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1221,6 +1286,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1276,6 +1346,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Serra</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1331,6 +1406,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1386,6 +1466,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1441,6 +1526,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1496,6 +1586,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1551,6 +1646,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Venda Nova do Imigrante</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1606,6 +1706,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1661,6 +1766,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1716,6 +1826,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1771,6 +1886,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1826,6 +1946,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Guarapari</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1881,6 +2006,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1936,6 +2066,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ibatiba</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1991,6 +2126,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Nova Venécia</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2046,6 +2186,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2101,6 +2246,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2156,6 +2306,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Linhares</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2211,6 +2366,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Serra</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2266,6 +2426,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Cachoeiro de Itapemirim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2321,6 +2486,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Piúma</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2376,6 +2546,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2431,6 +2606,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Guarapari</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2486,6 +2666,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>São Mateus</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2541,6 +2726,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2596,6 +2786,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Aracruz</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2651,6 +2846,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Cachoeiro de Itapemirim</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2706,6 +2906,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>São Mateus</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2761,6 +2966,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2816,6 +3026,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2871,6 +3086,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2926,6 +3146,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2981,6 +3206,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3036,6 +3266,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3091,6 +3326,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Nova Venécia</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3146,6 +3386,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Nova Venécia</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3201,6 +3446,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Montanha</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3256,6 +3506,11 @@
           <t>Em extinção</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3311,6 +3566,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3366,6 +3626,11 @@
           <t>Em extinção</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3421,6 +3686,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3476,6 +3746,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Venda Nova do Imigrante</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3531,6 +3806,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3586,6 +3866,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3641,6 +3926,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Viana</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3696,6 +3986,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3751,6 +4046,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Cachoeiro de Itapemirim</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3806,6 +4106,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3861,6 +4166,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3916,6 +4226,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3971,6 +4286,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4026,6 +4346,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Ibatiba</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4081,6 +4406,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4136,6 +4466,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4191,6 +4526,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4238,6 +4578,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Aracruz</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4285,6 +4630,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4340,6 +4690,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4395,6 +4750,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Aracruz</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4450,6 +4810,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4505,6 +4870,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4560,6 +4930,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Serra</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4615,6 +4990,11 @@
           <t>Em extinção</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4670,6 +5050,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4725,6 +5110,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Cachoeiro de Itapemirim</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4780,6 +5170,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4835,6 +5230,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Serra</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4890,6 +5290,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4945,6 +5350,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4998,6 +5408,11 @@
       <c r="K83" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Colatina</t>
         </is>
       </c>
     </row>

--- a/Enade_2016_Ifes.xlsx
+++ b/Enade_2016_Ifes.xlsx
@@ -47786,7 +47786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47805,29 +47805,61 @@
           <t>Ano</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Inscritos</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Participantes</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Nota Bruta - FG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Nota Bruta - CE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1457344</v>
+        <v>1117583</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO</t>
+          <t>AGRONOMIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
+      </c>
+      <c r="D2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.75483870967742</v>
+      </c>
+      <c r="G2" t="n">
+        <v>63.98709677419355</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1319231</v>
+        <v>1103831</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO</t>
+          <t>AGRONOMIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -47835,1205 +47867,17 @@
           <t>2016</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1264959</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1595560</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1458011</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1376048</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1574036</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AGRONOMIA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1117583</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AGRONOMIA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1103831</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AGRONOMIA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>100666</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1666010</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>150129</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1103832</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>66691</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>89040</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AQUICULTURA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1181819</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ARQUITETURA E URBANISMO</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1457328</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BIOMEDICINA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1103907</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CAFEICULTURA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1319232</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CIÊNCIA E TECNOLOGIA DE ALIMENTOS</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1117313</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS AGRÍCOLAS</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1103909</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS BIOLÓGICAS</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>1288837</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS BIOLÓGICAS</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1103692</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS BIOLÓGICAS</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>1550806</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS DA NATUREZA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1637375</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS ECONÔMICAS</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1382551</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ENGENHARIA AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1457329</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ENGENHARIA CIVIL</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>1515614</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ENGENHARIA CIVIL</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1188402</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE AQUICULTURA</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1349075</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE CONTROLE E AUTOMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>102499</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE CONTROLE E AUTOMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>123260</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE MINAS</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1181820</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE PESCA</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>121880</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE PRODUÇÃO</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>1374889</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ENGENHARIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1477535</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ENGENHARIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>88399</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ENGENHARIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1319229</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ENGENHARIA MECÂNICA</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1181815</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ENGENHARIA MECÂNICA</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>123569</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ENGENHARIA MECÂNICA</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1341020</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>ENGENHARIA MECÂNICA</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>88396</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ENGENHARIA METALÚRGICA</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1660412</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>ENGENHARIA QUÍMICA</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>121884</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ENGENHARIA SANITÁRIA E AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>1127924</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FÍSICA</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>1288840</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>FÍSICA</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>1308687</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>GEOGRAFIA</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>1421000</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>GEOLOGIA</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>1443426</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>GESTÃO AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>123336</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>INFORMÁTICA</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>1704263</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>INFORMÁTICA</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>1179970</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>1704262</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>1365444</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>1127926</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>50017213</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>1330110</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>LOGÍSTICA</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>66694</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>1103657</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>MATEMÁTICA</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>108730</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>MATEMÁTICA</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>1691158</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>MEDICINA VETERINÁRIA</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>1693947</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>MEDICINA VETERINÁRIA</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>1319230</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>PEDAGOGIA</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>1617650</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>PEDAGOGIA</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>1457327</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>PEDAGOGIA</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>48223</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>PROCESSOS METALÚRGICOS</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>88403</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>PROCESSOS METALÚRGICOS</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>1117076</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>QUÍMICA</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>1127927</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>QUÍMICA</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>88401</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>QUÍMICA</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>1349076</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>QUÍMICA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1342675</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>QUÍMICA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>66681</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>REDES DE COMPUTADORES</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>83953</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>REDES DE COMPUTADORES</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>102494</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>SANEAMENTO AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>48225</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>SANEAMENTO AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>1270538</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>SISTEMAS DE INFORMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>1127925</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>SISTEMAS DE INFORMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>122845</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>SISTEMAS DE INFORMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>1607113</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>SISTEMAS PARA INTERNET</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>1595496</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>SISTEMAS PARA INTERNET</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>1488260</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>ZOOTECNIA</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
+      <c r="D3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F3" t="n">
+        <v>54.71818181818182</v>
+      </c>
+      <c r="G3" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Enade_2016_Ifes.xlsx
+++ b/Enade_2016_Ifes.xlsx
@@ -42,6 +42,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arq_31" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arq_32" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arq_3B" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arq_43" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26603,35 +26604,7339 @@
           <t>ABEXBCEDZACDZDCAABBBEDCEDED</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CO_CURSO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>QE_I01</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>QE_I02</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>QE_I03</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>QE_I04</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>QE_I05</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>QE_I06</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>QE_I07</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>QE_I08</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>QE_I09</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>QE_I10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>QE_I11</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>QE_I12</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>QE_I13</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>QE_I14</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>QE_I15</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>QE_I16</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>QE_I17</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>QE_I18</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>QE_I19</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>QE_I20</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>QE_I21</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>QE_I22</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>QE_I23</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>QE_I24</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>QE_I25</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>QE_I26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>29</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>31</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>31</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>31</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>31</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>31</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>31</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>32</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>32</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>32</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>32</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>32</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>32</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>32</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>32</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>32</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>32</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>32</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>32</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>32</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>32</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>32</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>32</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>32</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>32</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>32</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>32</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>32</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>32</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>32</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>32</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>32</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>32</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>32</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>32</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>32</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>32</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>32</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>32</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>32</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>32</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>32</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>32</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>32</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>32</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>32</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>32</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>32</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>32</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>32</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1117583</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>32</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>32</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>33</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1103831</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>42</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35968,15 +43273,6 @@
       <c r="AQ43" t="n">
         <v>100</v>
       </c>
-      <c r="AR43" t="inlineStr"/>
-      <c r="AS43" t="inlineStr"/>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AU43" t="inlineStr"/>
-      <c r="AV43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr"/>
-      <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -38065,10 +45361,6 @@
           <t>ABEXBCEDZACDZDCAABBBEDCEDED</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="n">
         <v>222</v>
       </c>
@@ -38102,31 +45394,6 @@
       <c r="AA55" t="n">
         <v>222</v>
       </c>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
-      <c r="AQ55" t="inlineStr"/>
-      <c r="AR55" t="inlineStr"/>
-      <c r="AS55" t="inlineStr"/>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AU55" t="inlineStr"/>
-      <c r="AV55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr"/>
-      <c r="AX55" t="inlineStr"/>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
